--- a/public/docs/Plantilla Diplomas y Actas.xlsx
+++ b/public/docs/Plantilla Diplomas y Actas.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{55E450A5-3F29-479B-BBE3-EF75DD352F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27EDE75A-3BB1-4892-A6B9-7A806ED4764C}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{55E450A5-3F29-479B-BBE3-EF75DD352F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{393729D5-BCD5-400A-99AE-B453EF3DA403}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="People" sheetId="1" r:id="rId1"/>
-    <sheet name="Parameters" sheetId="2" r:id="rId2"/>
+    <sheet name="Parameters" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Parameters!$C$2:$M$196</definedName>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="331">
   <si>
     <t>Obligatorio</t>
   </si>
@@ -1049,6 +1049,9 @@
   </si>
   <si>
     <t>Venezuela - RIF</t>
+  </si>
+  <si>
+    <t>Validación</t>
   </si>
 </sst>
 </file>
@@ -4442,11 +4445,8 @@
   <protectedRanges>
     <protectedRange sqref="W2 A3:AC390" name="Rango1"/>
   </protectedRanges>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1:S2" xr:uid="{958D334F-CFFE-42EF-8850-9B12DB380E07}">
-      <formula1>#REF!</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O3:O1048576" xr:uid="{E944ABE3-7207-4AC7-B637-1AD3A9AB7939}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1:S2 O3:O1048576" xr:uid="{958D334F-CFFE-42EF-8850-9B12DB380E07}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -4485,10 +4485,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="C2:N196"/>
+  <dimension ref="A1:N196"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.8984375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="10.5" customWidth="1"/>
+    <col min="1" max="1" width="10.5" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="10.5" customWidth="1"/>
     <col min="4" max="4" width="33.59765625" customWidth="1"/>
     <col min="5" max="6" width="10.5" customWidth="1"/>
     <col min="10" max="10" width="10.5" customWidth="1"/>
@@ -4496,11 +4497,16 @@
     <col min="13" max="13" width="48.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="H2" s="34"/>
       <c r="I2" s="34"/>
     </row>
-    <row r="3" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D3" s="1" t="s">
         <v>59</v>
       </c>
@@ -4523,7 +4529,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>64</v>
       </c>
@@ -4549,7 +4555,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>72</v>
       </c>
@@ -4575,7 +4581,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>64</v>
       </c>
@@ -4598,7 +4604,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="7" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>72</v>
       </c>
@@ -4615,7 +4621,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="8" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
         <v>87</v>
       </c>
@@ -4629,7 +4635,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
         <v>91</v>
       </c>
@@ -4643,7 +4649,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="10" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
         <v>95</v>
       </c>
@@ -4657,7 +4663,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
         <v>99</v>
       </c>
@@ -4674,7 +4680,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
         <v>104</v>
       </c>
@@ -4691,7 +4697,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="13" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
         <v>72</v>
       </c>
@@ -4711,7 +4717,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="14" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
         <v>64</v>
       </c>
@@ -4731,7 +4737,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
         <v>72</v>
       </c>
@@ -4751,7 +4757,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="16" spans="3:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
         <v>64</v>
       </c>
@@ -5955,6 +5961,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_activity xmlns="d3fe6e8b-e724-4ddb-b4b3-18c8feb62e71" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101000A28CDC7F7405B409AF07461993E642D" ma:contentTypeVersion="18" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="b310fb61144ed1aff5e1e8d87a909888">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns3="d3fe6e8b-e724-4ddb-b4b3-18c8feb62e71" xmlns:ns4="43a0f58c-2e93-4dab-bfee-d08f43166e26" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0e19b1108e757d3feb26e37d1b57f48a" ns1:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6210,41 +6235,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_activity xmlns="d3fe6e8b-e724-4ddb-b4b3-18c8feb62e71" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42315591-C9C4-48BB-AF99-511E422C3B9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0288B4E2-BDE0-4170-915C-8123093118B8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="d3fe6e8b-e724-4ddb-b4b3-18c8feb62e71"/>
-    <ds:schemaRef ds:uri="43a0f58c-2e93-4dab-bfee-d08f43166e26"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6268,9 +6262,21 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0288B4E2-BDE0-4170-915C-8123093118B8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42315591-C9C4-48BB-AF99-511E422C3B9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="d3fe6e8b-e724-4ddb-b4b3-18c8feb62e71"/>
+    <ds:schemaRef ds:uri="43a0f58c-2e93-4dab-bfee-d08f43166e26"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/public/docs/Plantilla Diplomas y Actas.xlsx
+++ b/public/docs/Plantilla Diplomas y Actas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{55E450A5-3F29-479B-BBE3-EF75DD352F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{393729D5-BCD5-400A-99AE-B453EF3DA403}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{55E450A5-3F29-479B-BBE3-EF75DD352F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7E6D80E-6DE3-45D8-AD3C-1C51F9E71C4D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4032,7 +4032,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.8984375" style="4" customWidth="1"/>
@@ -4244,208 +4244,12 @@
     <row r="3" spans="1:29" ht="16.8" x14ac:dyDescent="0.3">
       <c r="D3" s="33"/>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="E4" s="7" t="str">
-        <f>IFERROR(VLOOKUP(O4,Parameters!C:D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="Q4" s="5" t="str">
-        <f>IF(_xlfn.XLOOKUP(People!$R4,Parameters!N:N,Parameters!M:M)=0,"",_xlfn.XLOOKUP(People!$R4,Parameters!N:N,Parameters!M:M))</f>
-        <v/>
-      </c>
-      <c r="S4" s="5" t="str">
-        <f>IFERROR(IF(_xlfn.XLOOKUP(R4,Parameters!N:N,Parameters!L:L)=0,"",_xlfn.XLOOKUP(R4,Parameters!N:N,Parameters!L:L)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="E5" s="7" t="str">
-        <f>IFERROR(VLOOKUP(O5,Parameters!C:D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="Q5" s="5" t="str">
-        <f>IF(_xlfn.XLOOKUP(People!$R5,Parameters!N:N,Parameters!M:M)=0,"",_xlfn.XLOOKUP(People!$R5,Parameters!N:N,Parameters!M:M))</f>
-        <v/>
-      </c>
-      <c r="S5" s="5" t="str">
-        <f>IFERROR(IF(_xlfn.XLOOKUP(R5,Parameters!N:N,Parameters!L:L)=0,"",_xlfn.XLOOKUP(R5,Parameters!N:N,Parameters!L:L)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="E6" s="7" t="str">
-        <f>IFERROR(VLOOKUP(O6,Parameters!C:D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="Q6" s="5" t="str">
-        <f>IF(_xlfn.XLOOKUP(People!$R6,Parameters!N:N,Parameters!M:M)=0,"",_xlfn.XLOOKUP(People!$R6,Parameters!N:N,Parameters!M:M))</f>
-        <v/>
-      </c>
-      <c r="S6" s="5" t="str">
-        <f>IFERROR(IF(_xlfn.XLOOKUP(R6,Parameters!N:N,Parameters!L:L)=0,"",_xlfn.XLOOKUP(R6,Parameters!N:N,Parameters!L:L)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="E7" s="7" t="str">
-        <f>IFERROR(VLOOKUP(O7,Parameters!C:D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="Q7" s="5" t="str">
-        <f>IF(_xlfn.XLOOKUP(People!$R7,Parameters!N:N,Parameters!M:M)=0,"",_xlfn.XLOOKUP(People!$R7,Parameters!N:N,Parameters!M:M))</f>
-        <v/>
-      </c>
-      <c r="S7" s="5" t="str">
-        <f>IFERROR(IF(_xlfn.XLOOKUP(R7,Parameters!N:N,Parameters!L:L)=0,"",_xlfn.XLOOKUP(R7,Parameters!N:N,Parameters!L:L)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="E8" s="7" t="str">
-        <f>IFERROR(VLOOKUP(O8,Parameters!C:D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="Q8" s="5" t="str">
-        <f>IF(_xlfn.XLOOKUP(People!$R8,Parameters!N:N,Parameters!M:M)=0,"",_xlfn.XLOOKUP(People!$R8,Parameters!N:N,Parameters!M:M))</f>
-        <v/>
-      </c>
-      <c r="S8" s="5" t="str">
-        <f>IFERROR(IF(_xlfn.XLOOKUP(R8,Parameters!N:N,Parameters!L:L)=0,"",_xlfn.XLOOKUP(R8,Parameters!N:N,Parameters!L:L)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="E9" s="7" t="str">
-        <f>IFERROR(VLOOKUP(O9,Parameters!C:D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="Q9" s="5" t="str">
-        <f>IF(_xlfn.XLOOKUP(People!$R9,Parameters!N:N,Parameters!M:M)=0,"",_xlfn.XLOOKUP(People!$R9,Parameters!N:N,Parameters!M:M))</f>
-        <v/>
-      </c>
-      <c r="S9" s="5" t="str">
-        <f>IFERROR(IF(_xlfn.XLOOKUP(R9,Parameters!N:N,Parameters!L:L)=0,"",_xlfn.XLOOKUP(R9,Parameters!N:N,Parameters!L:L)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="E10" s="7" t="str">
-        <f>IFERROR(VLOOKUP(O10,Parameters!C:D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="Q10" s="5" t="str">
-        <f>IF(_xlfn.XLOOKUP(People!$R10,Parameters!N:N,Parameters!M:M)=0,"",_xlfn.XLOOKUP(People!$R10,Parameters!N:N,Parameters!M:M))</f>
-        <v/>
-      </c>
-      <c r="S10" s="5" t="str">
-        <f>IFERROR(IF(_xlfn.XLOOKUP(R10,Parameters!N:N,Parameters!L:L)=0,"",_xlfn.XLOOKUP(R10,Parameters!N:N,Parameters!L:L)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="E11" s="7" t="str">
-        <f>IFERROR(VLOOKUP(O11,Parameters!C:D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="Q11" s="5" t="str">
-        <f>IF(_xlfn.XLOOKUP(People!$R11,Parameters!N:N,Parameters!M:M)=0,"",_xlfn.XLOOKUP(People!$R11,Parameters!N:N,Parameters!M:M))</f>
-        <v/>
-      </c>
-      <c r="S11" s="5" t="str">
-        <f>IFERROR(IF(_xlfn.XLOOKUP(R11,Parameters!N:N,Parameters!L:L)=0,"",_xlfn.XLOOKUP(R11,Parameters!N:N,Parameters!L:L)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="E12" s="7" t="str">
-        <f>IFERROR(VLOOKUP(O12,Parameters!C:D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="Q12" s="5" t="str">
-        <f>IF(_xlfn.XLOOKUP(People!$R12,Parameters!N:N,Parameters!M:M)=0,"",_xlfn.XLOOKUP(People!$R12,Parameters!N:N,Parameters!M:M))</f>
-        <v/>
-      </c>
-      <c r="S12" s="5" t="str">
-        <f>IFERROR(IF(_xlfn.XLOOKUP(R12,Parameters!N:N,Parameters!L:L)=0,"",_xlfn.XLOOKUP(R12,Parameters!N:N,Parameters!L:L)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="E13" s="7" t="str">
-        <f>IFERROR(VLOOKUP(O13,Parameters!C:D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="Q13" s="5" t="str">
-        <f>IF(_xlfn.XLOOKUP(People!$R13,Parameters!N:N,Parameters!M:M)=0,"",_xlfn.XLOOKUP(People!$R13,Parameters!N:N,Parameters!M:M))</f>
-        <v/>
-      </c>
-      <c r="S13" s="5" t="str">
-        <f>IFERROR(IF(_xlfn.XLOOKUP(R13,Parameters!N:N,Parameters!L:L)=0,"",_xlfn.XLOOKUP(R13,Parameters!N:N,Parameters!L:L)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="E14" s="7" t="str">
-        <f>IFERROR(VLOOKUP(O14,Parameters!C:D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="Q14" s="5" t="str">
-        <f>IF(_xlfn.XLOOKUP(People!$R14,Parameters!N:N,Parameters!M:M)=0,"",_xlfn.XLOOKUP(People!$R14,Parameters!N:N,Parameters!M:M))</f>
-        <v/>
-      </c>
-      <c r="S14" s="5" t="str">
-        <f>IFERROR(IF(_xlfn.XLOOKUP(R14,Parameters!N:N,Parameters!L:L)=0,"",_xlfn.XLOOKUP(R14,Parameters!N:N,Parameters!L:L)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="E15" s="7" t="str">
-        <f>IFERROR(VLOOKUP(O15,Parameters!C:D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="Q15" s="5" t="str">
-        <f>IF(_xlfn.XLOOKUP(People!$R15,Parameters!N:N,Parameters!M:M)=0,"",_xlfn.XLOOKUP(People!$R15,Parameters!N:N,Parameters!M:M))</f>
-        <v/>
-      </c>
-      <c r="S15" s="5" t="str">
-        <f>IFERROR(IF(_xlfn.XLOOKUP(R15,Parameters!N:N,Parameters!L:L)=0,"",_xlfn.XLOOKUP(R15,Parameters!N:N,Parameters!L:L)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="E16" s="7" t="str">
-        <f>IFERROR(VLOOKUP(O16,Parameters!C:D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="Q16" s="5" t="str">
-        <f>IF(_xlfn.XLOOKUP(People!$R16,Parameters!N:N,Parameters!M:M)=0,"",_xlfn.XLOOKUP(People!$R16,Parameters!N:N,Parameters!M:M))</f>
-        <v/>
-      </c>
-      <c r="S16" s="5" t="str">
-        <f>IFERROR(IF(_xlfn.XLOOKUP(R16,Parameters!N:N,Parameters!L:L)=0,"",_xlfn.XLOOKUP(R16,Parameters!N:N,Parameters!L:L)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="5:19" x14ac:dyDescent="0.3">
-      <c r="E17" s="7" t="str">
-        <f>IFERROR(VLOOKUP(O17,Parameters!C:D,2,FALSE),"")</f>
-        <v/>
-      </c>
-      <c r="Q17" s="5" t="str">
-        <f>IF(_xlfn.XLOOKUP(People!$R17,Parameters!N:N,Parameters!M:M)=0,"",_xlfn.XLOOKUP(People!$R17,Parameters!N:N,Parameters!M:M))</f>
-        <v/>
-      </c>
-      <c r="S17" s="5" t="str">
-        <f>IFERROR(IF(_xlfn.XLOOKUP(R17,Parameters!N:N,Parameters!L:L)=0,"",_xlfn.XLOOKUP(R17,Parameters!N:N,Parameters!L:L)),"")</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="qdwEOllK3iRysMnd02QmsWVWKuxY1mUskfsLDNoXZgdPDwPYE4y6Yy/r69KBb6PBSm6xGjzMD0uqMO3ncoOKxA==" saltValue="spXa7jPYsz0pNs23H7u3pg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="W2 A3:AC390" name="Rango1"/>
   </protectedRanges>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1:S2 O3:O1048576" xr:uid="{958D334F-CFFE-42EF-8850-9B12DB380E07}">
       <formula1>#REF!</formula1>
     </dataValidation>
@@ -4455,7 +4259,7 @@
   <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>Parameters!$F$4:$F$5</xm:f>
@@ -5961,25 +5765,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_activity xmlns="d3fe6e8b-e724-4ddb-b4b3-18c8feb62e71" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101000A28CDC7F7405B409AF07461993E642D" ma:contentTypeVersion="18" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="b310fb61144ed1aff5e1e8d87a909888">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns3="d3fe6e8b-e724-4ddb-b4b3-18c8feb62e71" xmlns:ns4="43a0f58c-2e93-4dab-bfee-d08f43166e26" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0e19b1108e757d3feb26e37d1b57f48a" ns1:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -6235,10 +6020,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <_activity xmlns="d3fe6e8b-e724-4ddb-b4b3-18c8feb62e71" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0288B4E2-BDE0-4170-915C-8123093118B8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42315591-C9C4-48BB-AF99-511E422C3B9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="d3fe6e8b-e724-4ddb-b4b3-18c8feb62e71"/>
+    <ds:schemaRef ds:uri="43a0f58c-2e93-4dab-bfee-d08f43166e26"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -6262,21 +6078,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{42315591-C9C4-48BB-AF99-511E422C3B9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0288B4E2-BDE0-4170-915C-8123093118B8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="d3fe6e8b-e724-4ddb-b4b3-18c8feb62e71"/>
-    <ds:schemaRef ds:uri="43a0f58c-2e93-4dab-bfee-d08f43166e26"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/public/docs/Plantilla Diplomas y Actas.xlsx
+++ b/public/docs/Plantilla Diplomas y Actas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{55E450A5-3F29-479B-BBE3-EF75DD352F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7E6D80E-6DE3-45D8-AD3C-1C51F9E71C4D}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{7ACA1682-4B7C-4415-8C63-6D8C5B028615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D7848C3-A45B-4FEC-A589-E3A5F8385B74}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="330">
   <si>
     <t>Obligatorio</t>
   </si>
@@ -97,14 +97,6 @@
   </si>
   <si>
     <t>Opcional
-Titulo</t>
-  </si>
-  <si>
-    <t>Opcional
-Programa</t>
-  </si>
-  <si>
-    <t>Opcional
 Programa Código y fecha</t>
   </si>
   <si>
@@ -196,9 +188,6 @@
     <t>lugarexpi</t>
   </si>
   <si>
-    <t>titulo</t>
-  </si>
-  <si>
     <t>programa</t>
   </si>
   <si>
@@ -1052,13 +1041,20 @@
   </si>
   <si>
     <t>Validación</t>
+  </si>
+  <si>
+    <t>titulograd</t>
+  </si>
+  <si>
+    <t>Opcional
+Titulo Grado</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -1102,12 +1098,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0078D7"/>
-      <name val="Segoe UI"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1325,7 +1315,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1420,9 +1410,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2178,13 +2165,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2276,13 +2263,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>21</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2374,13 +2361,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>22</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -2472,13 +2459,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
@@ -2554,13 +2541,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>23</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -2636,13 +2623,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -2718,13 +2705,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>23</xdr:col>
       <xdr:colOff>792480</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
+      <xdr:col>25</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -2800,14 +2787,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
+      <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>1507434</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -2824,8 +2811,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8991600" y="466165"/>
-          <a:ext cx="1497106" cy="448235"/>
+          <a:off x="17865587" y="0"/>
+          <a:ext cx="1507434" cy="447261"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2990,13 +2977,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>792480</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>220980</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>27</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
@@ -3072,13 +3059,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -3174,13 +3161,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -3272,13 +3259,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>6240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>211980</xdr:rowOff>
@@ -3354,13 +3341,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>27</xdr:col>
+      <xdr:col>26</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>6239</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>448234</xdr:rowOff>
@@ -3453,13 +3440,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>28</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>6240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>211980</xdr:rowOff>
@@ -3535,13 +3522,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>28</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>6239</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
+      <xdr:col>28</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>448234</xdr:rowOff>
@@ -3621,104 +3608,6 @@
               <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
             </a:rPr>
             <a:t>)</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-CO" sz="1100" b="0">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-            <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="CuadroTexto 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B258A268-19A1-4AC1-AAD1-DB3BEEDA4004}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="12129247" y="466165"/>
-          <a:ext cx="2241177" cy="448235"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="accent1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="ctr" anchorCtr="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-CO" sz="1100" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>PROGRAMA ACADÉMICO</a:t>
-          </a:r>
-          <a:br>
-            <a:rPr lang="es-CO" sz="1100" b="1" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-          </a:br>
-          <a:r>
-            <a:rPr lang="es-CO" sz="1100" b="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos" panose="020B0004020202020204" pitchFamily="34" charset="0"/>
-            </a:rPr>
-            <a:t>(Elija)</a:t>
           </a:r>
           <a:endParaRPr lang="es-CO" sz="1100" b="0">
             <a:solidFill>
@@ -4032,38 +3921,37 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.8984375" style="4" customWidth="1"/>
     <col min="2" max="2" width="22.09765625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="24" style="8" customWidth="1"/>
-    <col min="4" max="4" width="27.8984375" style="6" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" style="7" customWidth="1"/>
-    <col min="6" max="6" width="22.09765625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="22.59765625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="26.296875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="27.296875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="20.8984375" style="8" customWidth="1"/>
     <col min="7" max="7" width="21.59765625" style="5" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="8.3984375" style="7" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="10.5" style="7" hidden="1" customWidth="1"/>
     <col min="10" max="13" width="8.3984375" style="7" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="13.59765625" style="7" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="19.69921875" style="21" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="19.69921875" style="21" customWidth="1"/>
     <col min="16" max="16" width="21.19921875" style="5" customWidth="1"/>
-    <col min="17" max="17" width="13.5" style="5" hidden="1" customWidth="1"/>
-    <col min="18" max="18" width="43.3984375" style="5" customWidth="1"/>
-    <col min="19" max="19" width="29.59765625" style="5" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="28.5" style="5" customWidth="1"/>
-    <col min="21" max="21" width="31.3984375" style="5" customWidth="1"/>
-    <col min="22" max="22" width="34" style="5" customWidth="1"/>
-    <col min="23" max="23" width="31.3984375" style="5" customWidth="1"/>
-    <col min="24" max="24" width="9.69921875" style="10" customWidth="1"/>
-    <col min="25" max="26" width="9.69921875" style="11" customWidth="1"/>
-    <col min="27" max="27" width="9.69921875" style="9" customWidth="1"/>
-    <col min="28" max="28" width="26.8984375" style="13" customWidth="1"/>
-    <col min="29" max="29" width="43.19921875" style="12" customWidth="1"/>
-    <col min="30" max="16384" width="10.5" style="2"/>
+    <col min="17" max="17" width="31.69921875" style="5" customWidth="1"/>
+    <col min="18" max="18" width="29.59765625" style="5" customWidth="1"/>
+    <col min="19" max="19" width="28.5" style="5" customWidth="1"/>
+    <col min="20" max="20" width="31.3984375" style="5" customWidth="1"/>
+    <col min="21" max="21" width="34" style="5" customWidth="1"/>
+    <col min="22" max="22" width="31.3984375" style="5" customWidth="1"/>
+    <col min="23" max="23" width="9.69921875" style="10" customWidth="1"/>
+    <col min="24" max="25" width="9.69921875" style="11" customWidth="1"/>
+    <col min="26" max="26" width="9.69921875" style="9" customWidth="1"/>
+    <col min="27" max="27" width="26.8984375" style="13" customWidth="1"/>
+    <col min="28" max="28" width="43.19921875" style="12" customWidth="1"/>
+    <col min="29" max="16384" width="10.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="36.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:28" ht="36.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -4113,144 +4001,135 @@
         <v>15</v>
       </c>
       <c r="Q1" s="27" t="s">
+        <v>329</v>
+      </c>
+      <c r="R1" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="27" t="s">
+      <c r="S1" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="29" t="s">
+      <c r="T1" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="29" t="s">
+      <c r="U1" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="27" t="s">
+      <c r="V1" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="27" t="s">
+      <c r="W1" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="27" t="s">
+      <c r="X1" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="30" t="s">
+      <c r="Y1" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="31" t="s">
+      <c r="Z1" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="31" t="s">
+      <c r="AA1" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="30" t="s">
+      <c r="AB1" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="29" t="s">
+    </row>
+    <row r="2" spans="1:28" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="32" t="s">
+      <c r="B2" s="14" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="C2" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="D2" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="E2" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="F2" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="G2" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="H2" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="I2" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="J2" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="K2" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="L2" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="M2" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="N2" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="O2" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="N2" s="17" t="s">
+      <c r="P2" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="Q2" s="14" t="s">
+        <v>328</v>
+      </c>
+      <c r="R2" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="S2" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="T2" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="R2" s="14" t="s">
+      <c r="U2" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="S2" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="T2" s="15" t="s">
+      <c r="V2" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="U2" s="18" t="s">
+      <c r="W2" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="V2" s="14" t="s">
+      <c r="X2" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="W2" s="18" t="s">
+      <c r="Y2" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="X2" s="15" t="s">
+      <c r="Z2" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="Y2" s="19" t="s">
+      <c r="AA2" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="Z2" s="19" t="s">
+      <c r="AB2" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="AA2" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="AB2" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="AC2" s="20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:29" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="D3" s="33"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="qdwEOllK3iRysMnd02QmsWVWKuxY1mUskfsLDNoXZgdPDwPYE4y6Yy/r69KBb6PBSm6xGjzMD0uqMO3ncoOKxA==" saltValue="spXa7jPYsz0pNs23H7u3pg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="tlLyxLI3hG3mCyga15bGXgvylaC4Djtpjnxm0M18dNrEYn9x/tJ+yLAyHJRiy/5otMo+G1XqADwSqVzEAKXFOA==" saltValue="/JRoI+v4afQub62wm0RrwQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
-    <protectedRange sqref="W2 A3:AC390" name="Rango1"/>
+    <protectedRange sqref="V2 A3:AB390" name="Rango1"/>
   </protectedRanges>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S1:S2 O3:O1048576" xr:uid="{958D334F-CFFE-42EF-8850-9B12DB380E07}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R1:R2" xr:uid="{958D334F-CFFE-42EF-8850-9B12DB380E07}">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>
@@ -4259,7 +4138,7 @@
   <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="5">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>Parameters!$F$4:$F$5</xm:f>
@@ -4269,17 +4148,29 @@
           </x14:formula2>
           <xm:sqref>I3</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{536015C6-980D-49AD-AA84-70DF4D88498E}">
-          <x14:formula1>
-            <xm:f>Parameters!$N$4:$N$21</xm:f>
-          </x14:formula1>
-          <xm:sqref>R3:R1048576</xm:sqref>
-        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A6C488DF-6AA2-4CA9-A6C1-F047E0F38674}">
           <x14:formula1>
             <xm:f>Parameters!$D$4:$D$238</xm:f>
           </x14:formula1>
           <xm:sqref>E1:E1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2A5EC2BD-1CDF-4780-B1B3-87EE75BB312C}">
+          <x14:formula1>
+            <xm:f>Parameters!$H$4:$H$5</xm:f>
+          </x14:formula1>
+          <xm:sqref>O3:O1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DAC62D54-785C-41A3-9650-E9929EF0EF2A}">
+          <x14:formula1>
+            <xm:f>Parameters!$M$4:$M$21</xm:f>
+          </x14:formula1>
+          <xm:sqref>Q3:Q1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CE2FCC01-25DB-47C5-AC8A-2E45ACD767B5}">
+          <x14:formula1>
+            <xm:f>Parameters!$L$4:$L$21</xm:f>
+          </x14:formula1>
+          <xm:sqref>R3:R1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4299,1453 +4190,1454 @@
     <col min="10" max="10" width="10.5" customWidth="1"/>
     <col min="12" max="12" width="31" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="48.19921875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="48.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" t="s">
+        <v>58</v>
+      </c>
+      <c r="L3" t="s">
+        <v>43</v>
+      </c>
+      <c r="M3" t="s">
         <v>59</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="N3" t="s">
         <v>60</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J3" t="s">
-        <v>61</v>
-      </c>
-      <c r="L3" t="s">
-        <v>46</v>
-      </c>
-      <c r="M3" t="s">
-        <v>62</v>
-      </c>
-      <c r="N3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" t="s">
         <v>64</v>
       </c>
-      <c r="D4" t="s">
+      <c r="J4" t="s">
         <v>65</v>
       </c>
-      <c r="F4" t="s">
+      <c r="L4" t="s">
         <v>66</v>
       </c>
-      <c r="H4" t="s">
+      <c r="M4" t="s">
         <v>67</v>
       </c>
-      <c r="J4" t="s">
+      <c r="N4" t="s">
         <v>68</v>
-      </c>
-      <c r="L4" t="s">
-        <v>69</v>
-      </c>
-      <c r="M4" t="s">
-        <v>70</v>
-      </c>
-      <c r="N4" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H5" t="s">
+        <v>69</v>
+      </c>
+      <c r="J5" t="s">
         <v>72</v>
       </c>
-      <c r="D5" t="s">
+      <c r="L5" t="s">
         <v>73</v>
       </c>
-      <c r="F5" t="s">
-        <v>74</v>
-      </c>
-      <c r="H5" t="s">
-        <v>72</v>
-      </c>
-      <c r="J5" t="s">
-        <v>75</v>
-      </c>
-      <c r="L5" t="s">
-        <v>76</v>
-      </c>
       <c r="M5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H6" t="s">
+        <v>75</v>
+      </c>
+      <c r="J6" t="s">
+        <v>76</v>
+      </c>
+      <c r="L6" t="s">
         <v>77</v>
       </c>
-      <c r="H6" t="s">
+      <c r="M6" t="s">
         <v>78</v>
       </c>
-      <c r="J6" t="s">
+      <c r="N6" t="s">
         <v>79</v>
-      </c>
-      <c r="L6" t="s">
-        <v>80</v>
-      </c>
-      <c r="M6" t="s">
-        <v>81</v>
-      </c>
-      <c r="N6" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
+        <v>80</v>
+      </c>
+      <c r="L7" t="s">
+        <v>81</v>
+      </c>
+      <c r="M7" t="s">
+        <v>82</v>
+      </c>
+      <c r="N7" t="s">
         <v>83</v>
-      </c>
-      <c r="L7" t="s">
-        <v>84</v>
-      </c>
-      <c r="M7" t="s">
-        <v>85</v>
-      </c>
-      <c r="N7" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
+        <v>84</v>
+      </c>
+      <c r="L8" t="s">
+        <v>85</v>
+      </c>
+      <c r="M8" t="s">
+        <v>86</v>
+      </c>
+      <c r="N8" t="s">
         <v>87</v>
-      </c>
-      <c r="L8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M8" t="s">
-        <v>89</v>
-      </c>
-      <c r="N8" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
+        <v>88</v>
+      </c>
+      <c r="L9" t="s">
+        <v>89</v>
+      </c>
+      <c r="M9" t="s">
+        <v>90</v>
+      </c>
+      <c r="N9" t="s">
         <v>91</v>
-      </c>
-      <c r="L9" t="s">
-        <v>92</v>
-      </c>
-      <c r="M9" t="s">
-        <v>93</v>
-      </c>
-      <c r="N9" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
+        <v>92</v>
+      </c>
+      <c r="L10" t="s">
+        <v>93</v>
+      </c>
+      <c r="M10" t="s">
+        <v>94</v>
+      </c>
+      <c r="N10" t="s">
         <v>95</v>
-      </c>
-      <c r="L10" t="s">
-        <v>96</v>
-      </c>
-      <c r="M10" t="s">
-        <v>97</v>
-      </c>
-      <c r="N10" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F11" t="s">
+        <v>97</v>
+      </c>
+      <c r="L11" t="s">
+        <v>98</v>
+      </c>
+      <c r="M11" t="s">
         <v>99</v>
       </c>
-      <c r="F11" t="s">
+      <c r="N11" t="s">
         <v>100</v>
-      </c>
-      <c r="L11" t="s">
-        <v>101</v>
-      </c>
-      <c r="M11" t="s">
-        <v>102</v>
-      </c>
-      <c r="N11" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F12" t="s">
+        <v>102</v>
+      </c>
+      <c r="L12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M12" t="s">
         <v>104</v>
       </c>
-      <c r="F12" t="s">
+      <c r="N12" t="s">
         <v>105</v>
-      </c>
-      <c r="L12" t="s">
-        <v>106</v>
-      </c>
-      <c r="M12" t="s">
-        <v>107</v>
-      </c>
-      <c r="N12" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
+        <v>106</v>
+      </c>
+      <c r="F13" t="s">
+        <v>107</v>
+      </c>
+      <c r="L13" t="s">
+        <v>108</v>
+      </c>
+      <c r="M13" t="s">
         <v>109</v>
       </c>
-      <c r="F13" t="s">
+      <c r="N13" t="s">
         <v>110</v>
-      </c>
-      <c r="L13" t="s">
-        <v>111</v>
-      </c>
-      <c r="M13" t="s">
-        <v>112</v>
-      </c>
-      <c r="N13" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
+        <v>111</v>
+      </c>
+      <c r="F14" t="s">
+        <v>112</v>
+      </c>
+      <c r="L14" t="s">
+        <v>113</v>
+      </c>
+      <c r="M14" t="s">
         <v>114</v>
       </c>
-      <c r="F14" t="s">
+      <c r="N14" t="s">
         <v>115</v>
-      </c>
-      <c r="L14" t="s">
-        <v>116</v>
-      </c>
-      <c r="M14" t="s">
-        <v>117</v>
-      </c>
-      <c r="N14" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C15" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F15" t="s">
+        <v>117</v>
+      </c>
+      <c r="L15" t="s">
+        <v>118</v>
+      </c>
+      <c r="M15" t="s">
         <v>119</v>
       </c>
-      <c r="F15" t="s">
+      <c r="N15" t="s">
         <v>120</v>
-      </c>
-      <c r="L15" t="s">
-        <v>121</v>
-      </c>
-      <c r="M15" t="s">
-        <v>122</v>
-      </c>
-      <c r="N15" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F16" t="s">
+        <v>122</v>
+      </c>
+      <c r="L16" t="s">
+        <v>123</v>
+      </c>
+      <c r="M16" t="s">
         <v>124</v>
       </c>
-      <c r="F16" t="s">
+      <c r="N16" t="s">
         <v>125</v>
-      </c>
-      <c r="L16" t="s">
-        <v>126</v>
-      </c>
-      <c r="M16" t="s">
-        <v>127</v>
-      </c>
-      <c r="N16" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="17" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s">
+        <v>126</v>
+      </c>
+      <c r="F17" t="s">
+        <v>127</v>
+      </c>
+      <c r="L17" t="s">
+        <v>128</v>
+      </c>
+      <c r="M17" t="s">
         <v>129</v>
       </c>
-      <c r="F17" t="s">
+      <c r="N17" t="s">
         <v>130</v>
-      </c>
-      <c r="L17" t="s">
-        <v>131</v>
-      </c>
-      <c r="M17" t="s">
-        <v>132</v>
-      </c>
-      <c r="N17" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="18" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D18" t="s">
+        <v>131</v>
+      </c>
+      <c r="F18" t="s">
+        <v>132</v>
+      </c>
+      <c r="L18" t="s">
+        <v>133</v>
+      </c>
+      <c r="M18" t="s">
         <v>134</v>
       </c>
-      <c r="F18" t="s">
+      <c r="N18" t="s">
         <v>135</v>
-      </c>
-      <c r="L18" t="s">
-        <v>136</v>
-      </c>
-      <c r="M18" t="s">
-        <v>137</v>
-      </c>
-      <c r="N18" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="19" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
+        <v>136</v>
+      </c>
+      <c r="F19" t="s">
+        <v>137</v>
+      </c>
+      <c r="L19" t="s">
+        <v>138</v>
+      </c>
+      <c r="M19" t="s">
         <v>139</v>
       </c>
-      <c r="F19" t="s">
+      <c r="N19" t="s">
         <v>140</v>
-      </c>
-      <c r="L19" t="s">
-        <v>141</v>
-      </c>
-      <c r="M19" t="s">
-        <v>142</v>
-      </c>
-      <c r="N19" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="20" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F20" t="s">
+        <v>142</v>
+      </c>
+      <c r="L20" t="s">
+        <v>143</v>
+      </c>
+      <c r="M20" t="s">
         <v>144</v>
       </c>
-      <c r="F20" t="s">
+      <c r="N20" t="s">
         <v>145</v>
-      </c>
-      <c r="L20" t="s">
-        <v>146</v>
-      </c>
-      <c r="M20" t="s">
-        <v>147</v>
-      </c>
-      <c r="N20" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="21" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D21" t="s">
+        <v>146</v>
+      </c>
+      <c r="F21" t="s">
+        <v>147</v>
+      </c>
+      <c r="L21" t="s">
+        <v>148</v>
+      </c>
+      <c r="M21" t="s">
         <v>149</v>
       </c>
-      <c r="F21" t="s">
+      <c r="N21" t="s">
         <v>150</v>
-      </c>
-      <c r="L21" t="s">
-        <v>151</v>
-      </c>
-      <c r="M21" t="s">
-        <v>152</v>
-      </c>
-      <c r="N21" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="22" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D22" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F22" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D23" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F23" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C24" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D24" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D25" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="3:14" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="3:14" x14ac:dyDescent="0.3">
       <c r="C32" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D32" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D33" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D34" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="36" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="37" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D37" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="38" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="39" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C39" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D39" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="40" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C41" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D41" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="42" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D42" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="43" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="45" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="46" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="47" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C47" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D47" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="48" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="49" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D49" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="51" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="52" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C52" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D52" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="53" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="54" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C54" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D54" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="55" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="56" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C56" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D56" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="57" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="58" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="59" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D59" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="60" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C60" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D60" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="61" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="62" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="63" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="64" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C64" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D64" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="65" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D65" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="66" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C66" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D66" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="67" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="68" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C68" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D68" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="69" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="70" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C70" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D70" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="71" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="72" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C72" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D72" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="73" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D73" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="74" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D74" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="75" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D75" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="76" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D76" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D77" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="78" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C78" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D78" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="79" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D79" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="80" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C80" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D80" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="81" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D81" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="82" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C82" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D82" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="83" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D83" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="84" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C84" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D84" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="85" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D85" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="86" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C86" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D86" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="87" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D87" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="88" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D88" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="89" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C89" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D89" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="90" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D90" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="91" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C91" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D91" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="92" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D92" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="93" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C93" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D93" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="94" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D94" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="95" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C95" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D95" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="96" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D96" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="97" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C97" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D97" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D98" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="99" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C99" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D99" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="100" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D100" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="101" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C101" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D101" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="102" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D102" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="103" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C103" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D103" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="104" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D104" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="105" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D105" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="106" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D106" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="107" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D107" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="108" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C108" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D108" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="109" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D109" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="110" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C110" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D110" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="111" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D111" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="112" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C112" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D112" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="113" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D113" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="114" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D114" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="115" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D115" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="116" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D116" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="117" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C117" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D117" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="118" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D118" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="119" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C119" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D119" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="120" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D120" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="121" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C121" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D121" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="122" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D122" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="123" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C123" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D123" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="124" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D124" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="125" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D125" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="126" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D126" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="127" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D127" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="128" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D128" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="129" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D129" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
     </row>
     <row r="130" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D130" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="131" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D131" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="132" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C132" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D132" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="133" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D133" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="134" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C134" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D134" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="135" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D135" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="136" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C136" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D136" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="137" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D137" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="138" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D138" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="139" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C139" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D139" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="140" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D140" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="141" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D141" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="142" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C142" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D142" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="143" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D143" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="144" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D144" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="145" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C145" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D145" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="146" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D146" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="147" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C147" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D147" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="148" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D148" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="149" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C149" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D149" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="150" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D150" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="151" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C151" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D151" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="152" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D152" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="153" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C153" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D153" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="154" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D154" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="155" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C155" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D155" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="156" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D156" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="157" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C157" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D157" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="158" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D158" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="159" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C159" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D159" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="160" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D160" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="161" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C161" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D161" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="162" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D162" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="163" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C163" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D163" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="164" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D164" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="165" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C165" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D165" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="166" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D166" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="167" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C167" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D167" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="168" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D168" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="169" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C169" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D169" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="170" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D170" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="171" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C171" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D171" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="172" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D172" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="173" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D173" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="174" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C174" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D174" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="175" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D175" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="176" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C176" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D176" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
     </row>
     <row r="177" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D177" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="178" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C178" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D178" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="179" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D179" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="180" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C180" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D180" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="181" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D181" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="182" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C182" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D182" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="183" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D183" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="184" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D184" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="185" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C185" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D185" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="186" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D186" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="187" spans="3:4" x14ac:dyDescent="0.3">
       <c r="C187" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D187" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="188" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D188" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="189" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D189" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="190" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D190" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="191" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D191" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="192" spans="3:4" x14ac:dyDescent="0.3">
       <c r="D192" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="193" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D193" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="194" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D194" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="195" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D195" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="196" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D196" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -6021,6 +5913,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -6028,15 +5929,6 @@
     <_activity xmlns="d3fe6e8b-e724-4ddb-b4b3-18c8feb62e71" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6060,6 +5952,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0288B4E2-BDE0-4170-915C-8123093118B8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E00AF4BB-C44E-4AD3-955F-7913542FB053}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -6075,12 +5975,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0288B4E2-BDE0-4170-915C-8123093118B8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>